--- a/Templates/创建属性模板.xlsx
+++ b/Templates/创建属性模板.xlsx
@@ -1,100 +1,172 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\开发\代码仓\EB\EBAssistant\Templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22188" windowHeight="9132"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
   <si>
     <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>属性名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>属性类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>test1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文本</t>
+  </si>
+  <si>
+    <t>注释1</t>
   </si>
   <si>
     <t>test2</t>
   </si>
   <si>
+    <t>注释2</t>
+  </si>
+  <si>
     <t>test3</t>
   </si>
   <si>
+    <t>注释3</t>
+  </si>
+  <si>
     <t>test4</t>
   </si>
   <si>
+    <t>注释4</t>
+  </si>
+  <si>
     <t>test5</t>
   </si>
   <si>
+    <t>注释5</t>
+  </si>
+  <si>
     <t>test6</t>
   </si>
   <si>
+    <t>注释6</t>
+  </si>
+  <si>
     <t>test7</t>
   </si>
   <si>
+    <t>注释7</t>
+  </si>
+  <si>
     <t>test8</t>
   </si>
   <si>
+    <t>注释8</t>
+  </si>
+  <si>
     <t>test9</t>
   </si>
   <si>
+    <t>注释9</t>
+  </si>
+  <si>
     <t>test10</t>
   </si>
   <si>
+    <t>注释10</t>
+  </si>
+  <si>
     <t>test11</t>
   </si>
   <si>
+    <t>注释11</t>
+  </si>
+  <si>
     <t>test12</t>
   </si>
   <si>
+    <t>注释12</t>
+  </si>
+  <si>
     <t>test13</t>
   </si>
   <si>
+    <t>注释13</t>
+  </si>
+  <si>
     <t>test14</t>
   </si>
   <si>
+    <t>注释14</t>
+  </si>
+  <si>
     <t>test15</t>
   </si>
   <si>
+    <t>注释15</t>
+  </si>
+  <si>
     <t>test16</t>
   </si>
   <si>
+    <t>注释16</t>
+  </si>
+  <si>
     <t>test17</t>
   </si>
   <si>
+    <t>注释17</t>
+  </si>
+  <si>
     <t>test18</t>
   </si>
   <si>
+    <t>注释18</t>
+  </si>
+  <si>
     <t>test19</t>
   </si>
   <si>
+    <t>注释19</t>
+  </si>
+  <si>
     <t>test20</t>
   </si>
   <si>
-    <t>文本</t>
+    <t>注释20</t>
+  </si>
+  <si>
+    <t>注释</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -107,13 +179,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -200,7 +271,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -235,7 +306,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -410,20 +481,15 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -433,8 +499,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -442,221 +511,281 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>4</v>
+      </c>
+      <c r="D21" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>